--- a/sampleprojects/CorporateTax/excel/states/VT_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/VT_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>DT: Determine VT Filing Requirement</t>
   </si>
@@ -148,19 +148,19 @@
     <t>Calculate VT tax using graduated brackets (6%, 7%, 8.5%); VT income tax using graduated rates: 6% up to $10K, 7% $10K-$25K, 8.5% over $25K</t>
   </si>
   <si>
-    <t>set apportionment.vt_calculated_tax = (the minimum of (apportionment.state_taxable_income) and (apportionment.vt_bracket_threshold_1)) * apportionment.vt_tax_rate_tier1; if apportionment.state_taxable_income &gt; apportionment.vt_bracket_threshold_1 then set apportionment.vt_calculated_tax = apportionment.vt_calculated_tax + ((the minimum of (apportionment.state_taxable_income) and (apportionment.vt_bracket_threshold_2)) - apportionment.vt_bracket_threshold_1) * apportionment.vt_tax_rate_tier2; endif if apportionment.state_taxable_income &gt; apportionment.vt_bracket_threshold_2 then set apportionment.vt_calculated_tax = apportionment.vt_calculated_tax + (apportionment.state_taxable_income - apportionment.vt_bracket_threshold_2) * apportionment.vt_tax_rate_tier3; endif set apportionment.state_tax = the maximum of (apportionment.vt_calculated_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "VT tax calculated using graduated brackets: 6% on first $10K, 7% on $10K-$25K, 8.5% over $25K (one of highest state rates). Reference: 32 V.S.A. 5832" to job.audit_trail;</t>
+    <t>set vt_apportionment.calculated_tax = (the minimum of (apportionment.state_taxable_income) and (vt_apportionment.bracket_threshold_1)) * vt_apportionment.tax_rate_tier1; if apportionment.state_taxable_income &gt; vt_apportionment.bracket_threshold_1 then set vt_apportionment.calculated_tax = vt_apportionment.calculated_tax + ((the minimum of (apportionment.state_taxable_income) and (vt_apportionment.bracket_threshold_2)) - vt_apportionment.bracket_threshold_1) * vt_apportionment.tax_rate_tier2; endif if apportionment.state_taxable_income &gt; vt_apportionment.bracket_threshold_2 then set vt_apportionment.calculated_tax = vt_apportionment.calculated_tax + (apportionment.state_taxable_income - vt_apportionment.bracket_threshold_2) * vt_apportionment.tax_rate_tier3; endif set apportionment.state_tax = the maximum of (vt_apportionment.calculated_tax - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax; add "VT tax calculated using graduated brackets: 6% on first $10K, 7% on $10K-$25K, 8.5% over $25K (one of highest state rates). Reference: 32 V.S.A. 5832" to job.audit_trail;</t>
   </si>
   <si>
     <t>No VT nexus - no tax liability; No VT nexus - no tax</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = 0.0; set apportionment.vt_calculated_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No VT nexus - no tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
+    <t>set apportionment.state_tax = 0.0; set vt_apportionment.calculated_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No VT nexus - no tax liability. Any estimated payments are refunded." to job.audit_trail;</t>
   </si>
   <si>
     <t>Nexus but no taxable income; No VT taxable income - no tax</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = 0.0; set apportionment.vt_calculated_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No VT taxable income - no tax. VT NOL rules may apply. Reference: 32 V.S.A. 5832" to job.audit_trail;</t>
+    <t>set apportionment.state_tax = 0.0; set vt_apportionment.calculated_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments; add "No VT taxable income - no tax. VT NOL rules may apply. Reference: 32 V.S.A. 5832" to job.audit_trail;</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(14 attributes)</t>
+    <t>vt_apportionment</t>
+  </si>
+  <si>
+    <t>(10 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -226,48 +226,45 @@
     <t>VT uses single-sales factor apportionment (100% sales factor)</t>
   </si>
   <si>
+    <t>bracket_threshold_1</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>10000.0</t>
+  </si>
+  <si>
+    <t>VT first bracket threshold: $10,000</t>
+  </si>
+  <si>
+    <t>bracket_threshold_2</t>
+  </si>
+  <si>
+    <t>25000.0</t>
+  </si>
+  <si>
+    <t>VT second bracket threshold: $25,000</t>
+  </si>
+  <si>
+    <t>calculated_tax</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>VT corporate tax calculated using graduated brackets (before credits)</t>
+  </si>
+  <si>
     <t>economic_nexus_threshold</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>100000.0</t>
   </si>
   <si>
     <t>VT economic nexus threshold: $100,000 (sales tax standard; income tax uses "doing business" test)</t>
   </si>
   <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>VT additions: federal interest income, certain expenses, state tax modifications, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t>Vermont state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>VT tax credits: R&amp;D, affordable housing, renewable energy, historic preservation, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>VT subtractions: VT municipal bond interest, state NOL, dividend deductions, etc.</t>
-  </si>
-  <si>
     <t>state_tax_rate</t>
   </si>
   <si>
@@ -277,6 +274,30 @@
     <t>VT top corporate income tax rate: 8.5% (one of highest state rates) - 32 V.S.A. § 5832</t>
   </si>
   <si>
+    <t>tax_rate_tier1</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>VT corporate tax rate tier 1: 6.0% on income $0-$10,000 - 32 V.S.A. § 5832</t>
+  </si>
+  <si>
+    <t>tax_rate_tier2</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>VT corporate tax rate tier 2: 7.0% on income $10,001-$25,000 - 32 V.S.A. § 5832</t>
+  </si>
+  <si>
+    <t>tax_rate_tier3</t>
+  </si>
+  <si>
+    <t>VT corporate tax rate tier 3: 8.5% on income over $25,000 - 32 V.S.A. § 5832</t>
+  </si>
+  <si>
     <t>transaction_threshold</t>
   </si>
   <si>
@@ -287,54 +308,6 @@
   </si>
   <si>
     <t>VT no longer uses transaction threshold (repealed July 1, 2022)</t>
-  </si>
-  <si>
-    <t>vt_bracket_threshold_1</t>
-  </si>
-  <si>
-    <t>10000.0</t>
-  </si>
-  <si>
-    <t>VT first bracket threshold: $10,000</t>
-  </si>
-  <si>
-    <t>vt_bracket_threshold_2</t>
-  </si>
-  <si>
-    <t>25000.0</t>
-  </si>
-  <si>
-    <t>VT second bracket threshold: $25,000</t>
-  </si>
-  <si>
-    <t>vt_calculated_tax</t>
-  </si>
-  <si>
-    <t>VT corporate tax calculated using graduated brackets (before credits)</t>
-  </si>
-  <si>
-    <t>vt_tax_rate_tier1</t>
-  </si>
-  <si>
-    <t>0.060</t>
-  </si>
-  <si>
-    <t>VT corporate tax rate tier 1: 6.0% on income $0-$10,000 - 32 V.S.A. § 5832</t>
-  </si>
-  <si>
-    <t>vt_tax_rate_tier2</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>VT corporate tax rate tier 2: 7.0% on income $10,001-$25,000 - 32 V.S.A. § 5832</t>
-  </si>
-  <si>
-    <t>vt_tax_rate_tier3</t>
-  </si>
-  <si>
-    <t>VT corporate tax rate tier 3: 8.5% on income over $25,000 - 32 V.S.A. § 5832</t>
   </si>
 </sst>
 </file>
@@ -2602,8 +2575,8 @@
       <c r="B7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>65</v>
+      <c r="C7" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
@@ -2650,7 +2623,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>14</v>
@@ -2659,7 +2632,7 @@
         <v>67</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>14</v>
@@ -2682,7 +2655,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>70</v>
@@ -2691,7 +2664,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>14</v>
@@ -2700,7 +2673,7 @@
         <v>67</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>14</v>
@@ -2723,7 +2696,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>70</v>
@@ -2732,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>14</v>
@@ -2741,7 +2714,7 @@
         <v>67</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>14</v>
@@ -2764,16 +2737,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>14</v>
@@ -2782,7 +2755,7 @@
         <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>14</v>
@@ -2805,7 +2778,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>70</v>
@@ -2814,7 +2787,7 @@
         <v>14</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>14</v>
@@ -2849,13 +2822,13 @@
         <v>93</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>14</v>
@@ -2864,7 +2837,7 @@
         <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>14</v>
@@ -2879,170 +2852,6 @@
         <v>14</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M17" s="8" t="s">
         <v>14</v>
       </c>
     </row>
